--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,8 +785,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101431605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101431605</v>
+        <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>79085</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillersmyren, Vrm</t>
+          <t>Svarttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398519</v>
+        <v>398534</v>
       </c>
       <c r="R2" t="n">
-        <v>6694015</v>
+        <v>6693859</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,24 +775,6743 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Grandin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Grandin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136078577</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136078592</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79475</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>398769</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6693960</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078592</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136078595</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79475</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>398786</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6693933</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078595</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136078620</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79475</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>398689</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6694002</v>
+      </c>
+      <c r="S5" t="n">
+        <v>11</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078620</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136078632</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79475</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>398541</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6693914</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078632</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136078603</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79109</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>398878</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6693962</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078603</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136078576</v>
+      </c>
+      <c r="B8" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>398534</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6693848</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078576</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136078590</v>
+      </c>
+      <c r="B9" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>398755</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6693979</v>
+      </c>
+      <c r="S9" t="n">
+        <v>99</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078590</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136078591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>398769</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6693958</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078591</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136078601</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>398869</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6693960</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078601</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136078622</v>
+      </c>
+      <c r="B12" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>398652</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6693989</v>
+      </c>
+      <c r="S12" t="n">
+        <v>18</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078622</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136078626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81425</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>398594</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6693984</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078626</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136078586</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>398713</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6693888</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078586</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136078587</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>398708</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6693879</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078587</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136078621</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>398665</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6693990</v>
+      </c>
+      <c r="S16" t="n">
+        <v>29</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078621</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136078628</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>398589</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6693974</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078628</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136078629</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93362</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>398592</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6693971</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078629</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136078575</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>398523</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6693836</v>
+      </c>
+      <c r="S19" t="n">
+        <v>22</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078575</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136078578</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>398533</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6693897</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078578</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136078579</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>398531</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6693907</v>
+      </c>
+      <c r="S21" t="n">
+        <v>24</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078579</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136078580</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>398555</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6693896</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078580</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136078581</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>398600</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6693917</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078581</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136078582</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>398617</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6693921</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078582</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136078589</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>398768</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6693959</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078589</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136078594</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>398782</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6693946</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078594</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136078596</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>398810</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6693924</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078596</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136078597</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>398830</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6693976</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078597</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136078599</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>398860</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6693982</v>
+      </c>
+      <c r="S29" t="n">
+        <v>16</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078599</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136078602</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>398868</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6693952</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078602</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136078605</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>398845</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6693917</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078605</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136078606</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>398837</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6693923</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078606</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136078610</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>398800</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6693983</v>
+      </c>
+      <c r="S33" t="n">
+        <v>22</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078610</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136078613</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>398801</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6694026</v>
+      </c>
+      <c r="S34" t="n">
+        <v>29</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078613</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136078615</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>398765</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6694014</v>
+      </c>
+      <c r="S35" t="n">
+        <v>12</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Garnlavstrassel</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078615</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136078616</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>398749</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6694008</v>
+      </c>
+      <c r="S36" t="n">
+        <v>22</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078616</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136078617</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>398737</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6694013</v>
+      </c>
+      <c r="S37" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078617</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136078625</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>398607</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6693989</v>
+      </c>
+      <c r="S38" t="n">
+        <v>13</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078625</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136078630</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>398598</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6693955</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078630</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>136078631</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>398573</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6693916</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078631</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136078635</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>398516</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6693890</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078635</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136078636</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79443</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>398470</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6693875</v>
+      </c>
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078636</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136078600</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79467</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>398868</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6693984</v>
+      </c>
+      <c r="S43" t="n">
+        <v>12</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078600</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136078584</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>398651</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6693875</v>
+      </c>
+      <c r="S44" t="n">
+        <v>9</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078584</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136078593</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>398782</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6693966</v>
+      </c>
+      <c r="S45" t="n">
+        <v>12</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078593</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136078608</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>398818</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6693964</v>
+      </c>
+      <c r="S46" t="n">
+        <v>14</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078608</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136078634</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79200</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>398532</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6693906</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078634</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136078588</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>398698</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6693892</v>
+      </c>
+      <c r="S48" t="n">
+        <v>13</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078588</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>136078598</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>398849</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6693969</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078598</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136078607</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>398815</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6693958</v>
+      </c>
+      <c r="S50" t="n">
+        <v>14</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078607</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>136078609</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>398808</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6693964</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078609</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>136078611</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>398824</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6693998</v>
+      </c>
+      <c r="S52" t="n">
+        <v>23</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078611</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>136078624</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>398645</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6693986</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078624</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136078627</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80062</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>398593</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6693973</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078627</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>136078574</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80558</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>398525</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6693854</v>
+      </c>
+      <c r="S55" t="n">
+        <v>17</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078574</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>136078573</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>398525</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6693854</v>
+      </c>
+      <c r="S56" t="n">
+        <v>17</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078573</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>136078612</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>398829</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6694004</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078612</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>101431605</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Gillersmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>398519</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6694015</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Fredrik Grandin</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Fredrik Grandin</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/101431605</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>136078614</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>398816</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6694039</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078614</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>136078619</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>398699</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6694007</v>
+      </c>
+      <c r="S60" t="n">
+        <v>13</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078619</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>136078623</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Svarttjärn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>398645</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6693986</v>
+      </c>
+      <c r="S61" t="n">
+        <v>6</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136078623</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136078592</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136078595</v>
       </c>
       <c r="B4" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136078620</v>
       </c>
       <c r="B5" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136078632</v>
       </c>
       <c r="B6" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136078603</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136078576</v>
       </c>
       <c r="B8" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136078590</v>
       </c>
       <c r="B9" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136078591</v>
       </c>
       <c r="B10" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136078601</v>
       </c>
       <c r="B11" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136078622</v>
       </c>
       <c r="B12" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136078626</v>
       </c>
       <c r="B13" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>136078575</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>136078578</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136078579</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136078580</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136078581</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136078582</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>136078589</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>136078594</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136078596</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>136078597</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136078599</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136078602</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136078605</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>136078606</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>136078610</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136078613</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136078615</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136078616</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>136078617</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136078625</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136078630</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>136078631</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>136078635</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>136078636</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>136078600</v>
       </c>
       <c r="B43" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136078584</v>
       </c>
       <c r="B44" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>136078593</v>
       </c>
       <c r="B45" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136078608</v>
       </c>
       <c r="B46" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136078634</v>
       </c>
       <c r="B47" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136078588</v>
       </c>
       <c r="B48" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>136078598</v>
       </c>
       <c r="B49" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>136078607</v>
       </c>
       <c r="B50" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>136078609</v>
       </c>
       <c r="B51" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136078611</v>
       </c>
       <c r="B52" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136078624</v>
       </c>
       <c r="B53" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136078627</v>
       </c>
       <c r="B54" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136078574</v>
       </c>
       <c r="B55" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>136078573</v>
       </c>
       <c r="B56" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>136078614</v>
       </c>
       <c r="B59" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136078619</v>
       </c>
       <c r="B60" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136078623</v>
       </c>
       <c r="B61" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136078592</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136078595</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136078620</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136078632</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136078603</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136078576</v>
       </c>
       <c r="B8" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136078590</v>
       </c>
       <c r="B9" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136078591</v>
       </c>
       <c r="B10" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136078601</v>
       </c>
       <c r="B11" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136078622</v>
       </c>
       <c r="B12" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136078626</v>
       </c>
       <c r="B13" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>136078575</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>136078578</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136078579</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136078580</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136078581</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136078582</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>136078589</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>136078594</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136078596</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>136078597</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136078599</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136078602</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136078605</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>136078606</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>136078610</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136078613</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136078615</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136078616</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>136078617</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136078625</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136078630</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>136078631</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>136078635</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>136078636</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>136078600</v>
       </c>
       <c r="B43" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136078584</v>
       </c>
       <c r="B44" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>136078593</v>
       </c>
       <c r="B45" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136078608</v>
       </c>
       <c r="B46" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136078634</v>
       </c>
       <c r="B47" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136078588</v>
       </c>
       <c r="B48" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>136078598</v>
       </c>
       <c r="B49" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>136078607</v>
       </c>
       <c r="B50" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>136078609</v>
       </c>
       <c r="B51" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136078611</v>
       </c>
       <c r="B52" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136078624</v>
       </c>
       <c r="B53" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136078627</v>
       </c>
       <c r="B54" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136078574</v>
       </c>
       <c r="B55" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>136078573</v>
       </c>
       <c r="B56" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>136078612</v>
       </c>
       <c r="B57" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>136078614</v>
       </c>
       <c r="B59" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136078619</v>
       </c>
       <c r="B60" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136078623</v>
       </c>
       <c r="B61" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136078592</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136078595</v>
       </c>
       <c r="B4" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136078620</v>
       </c>
       <c r="B5" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136078632</v>
       </c>
       <c r="B6" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136078603</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136078576</v>
       </c>
       <c r="B8" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136078590</v>
       </c>
       <c r="B9" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136078591</v>
       </c>
       <c r="B10" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136078601</v>
       </c>
       <c r="B11" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136078622</v>
       </c>
       <c r="B12" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136078626</v>
       </c>
       <c r="B13" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>136078575</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>136078578</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136078579</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136078580</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136078581</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136078582</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>136078589</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>136078594</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136078596</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>136078597</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136078599</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136078602</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136078605</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>136078606</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>136078610</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136078613</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136078615</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136078616</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>136078617</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136078625</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136078630</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>136078631</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>136078635</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>136078636</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>136078600</v>
       </c>
       <c r="B43" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136078584</v>
       </c>
       <c r="B44" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>136078593</v>
       </c>
       <c r="B45" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136078608</v>
       </c>
       <c r="B46" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136078634</v>
       </c>
       <c r="B47" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136078588</v>
       </c>
       <c r="B48" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>136078598</v>
       </c>
       <c r="B49" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>136078607</v>
       </c>
       <c r="B50" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>136078609</v>
       </c>
       <c r="B51" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136078611</v>
       </c>
       <c r="B52" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136078624</v>
       </c>
       <c r="B53" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136078627</v>
       </c>
       <c r="B54" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136078574</v>
       </c>
       <c r="B55" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>136078573</v>
       </c>
       <c r="B56" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>136078612</v>
       </c>
       <c r="B57" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>136078614</v>
       </c>
       <c r="B59" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136078619</v>
       </c>
       <c r="B60" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136078623</v>
       </c>
       <c r="B61" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 30108-2026 artfynd.xlsx
+++ b/artfynd/A 30108-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136078577</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136078592</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136078595</v>
       </c>
       <c r="B4" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136078620</v>
       </c>
       <c r="B5" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136078632</v>
       </c>
       <c r="B6" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136078603</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136078576</v>
       </c>
       <c r="B8" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136078590</v>
       </c>
       <c r="B9" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136078591</v>
       </c>
       <c r="B10" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136078601</v>
       </c>
       <c r="B11" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136078622</v>
       </c>
       <c r="B12" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136078626</v>
       </c>
       <c r="B13" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136078586</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>136078587</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>136078621</v>
       </c>
       <c r="B16" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>136078628</v>
       </c>
       <c r="B17" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136078629</v>
       </c>
       <c r="B18" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>136078575</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>136078578</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>136078579</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>136078580</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>136078581</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>136078582</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>136078589</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>136078594</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>136078596</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>136078597</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>136078599</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>136078602</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>136078605</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>136078606</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
         <v>136078610</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>136078613</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>136078615</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>136078616</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>136078617</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136078625</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136078630</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>136078631</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>136078635</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>136078636</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>136078600</v>
       </c>
       <c r="B43" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136078584</v>
       </c>
       <c r="B44" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>136078593</v>
       </c>
       <c r="B45" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>136078608</v>
       </c>
       <c r="B46" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>136078634</v>
       </c>
       <c r="B47" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>136078588</v>
       </c>
       <c r="B48" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>136078598</v>
       </c>
       <c r="B49" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>136078607</v>
       </c>
       <c r="B50" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>136078609</v>
       </c>
       <c r="B51" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>136078611</v>
       </c>
       <c r="B52" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>136078624</v>
       </c>
       <c r="B53" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>136078627</v>
       </c>
       <c r="B54" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>136078574</v>
       </c>
       <c r="B55" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>136078573</v>
       </c>
       <c r="B56" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>136078612</v>
       </c>
       <c r="B57" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>136078614</v>
       </c>
       <c r="B59" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>136078619</v>
       </c>
       <c r="B60" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>136078623</v>
       </c>
       <c r="B61" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
